--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ewong-c\Documents\UiPath\3DCA_Workflow\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5F3231-A009-4923-B723-754F4F6C6BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC4A076-DC6A-46F6-9445-65FBD70CB60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,7 +357,7 @@
     <t>People V. Wende</t>
   </si>
   <si>
-    <t>Certificate of Compliance,Word Count Certification,Word Count Certificate,Certificate of Length,Certificate of Counsel,Certification of Word Count,Brief Format Certification,Certificate of Word Count,Declaration Regarding Word Count,Statement of Word Count@Statement of Appealability@Table of Contents,Topical Index@Table of Authorities,Table of Authority,Table of Cases and Authorities@Statement of Facts,Statement of the Facts,Statement of the Case,Summary of Alleged Facts,Statements of Case and Procedural Facts@Proof of Service,Certificate of Service,Proof of Service by Mail and Email,Proof of Service by Mail,Proof of Service by Mail/Electronic Service,Declaration of Service,Declaration of Service by Mail,Proof of Service by Mail and Electronically,Brief Format Certification Pursuant to California Rules of Court 8.360,Declaration of Electronic Service and Service by U.S. Mail,Attorney's Certificate of Electronic Service and Service by Mail,Attorney's Certificate of Service,@Argument,Arguments</t>
+    <t>Certificate of Compliance,Word Count Certification,Word Count Certificate,Certificate of Length,Certificate of Counsel,Certification of Word Count,Brief Format Certification,Certificate of Word Count,Declaration Regarding Word Count,Statement of Word Count,Certification of Compliance,Certificate Of Appellate Counsel Pursuant To Rule 8.204(C)(1) And Rule 8.360(B) Of The California Rules Of Court@Statement of Appealability@Table of Contents,Topical Index@Table of Authorities,Table of Authority,Table of Cases and Authorities@Statement of Facts,Statement of the Facts,Statement of the Case,Summary of Alleged Facts,Statements of Case and Procedural Facts@Proof of Service,Certificate of Service,Proof of Service by Mail and Email,Proof of Service by Mail,Proof of Service by Mail/Electronic Service,Declaration of Service,Declaration of Service by Mail,Proof of Service by Mail and Electronically,Brief Format Certification Pursuant to California Rules of Court 8.360,Declaration of Electronic Service and Service by U.S. Mail,Attorney's Certificate of Electronic Service and Service by Mail,Attorney's Certificate of Service,@Argument,Arguments</t>
   </si>
 </sst>
 </file>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ewong-c\Documents\UiPath\3DCA_Workflow\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22CD0C3-A08E-4F4D-B0D2-BB8E334A159C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0B6CB1-D15C-4257-B0AB-3222502093B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="122">
   <si>
     <t>Name</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>C:\Users\ewong-c\Documents\UiPath\3DCA_Workflow\Data\Input\</t>
+  </si>
+  <si>
+    <t>BriefExportFolderPath</t>
+  </si>
+  <si>
+    <t>C:\Users\ewong-c\Documents\UiPath\3DCA_Workflow\Data\BriefExport\</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1022"/>
+  <dimension ref="A1:Z1023"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.54296875" customWidth="1"/>
@@ -946,294 +952,301 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" t="s">
-        <v>112</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="B23" s="5"/>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="101.5">
-      <c r="A25" s="5" t="s">
+    <row r="26" spans="1:3" ht="101.5">
+      <c r="A26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="14.5">
-      <c r="B26" s="3"/>
-    </row>
     <row r="27" spans="1:3" ht="14.5">
-      <c r="A27" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="6"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:3" ht="14.5">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" ht="14.5">
       <c r="A29" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="30" spans="1:3" ht="14.5">
       <c r="A30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" ht="14.5">
+      <c r="A31" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="145">
-      <c r="A31" s="5" t="s">
+    <row r="32" spans="1:3" ht="145">
+      <c r="A32" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="14.5">
-      <c r="A32" s="5" t="s">
+    <row r="33" spans="1:3" ht="14.5">
+      <c r="A33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B33" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="14.5">
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="1:3" ht="87">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:3" ht="14.5">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" ht="87">
+      <c r="A35" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.5">
-      <c r="A35" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:3" ht="14.5">
       <c r="A36" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>86</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C36" s="5"/>
     </row>
     <row r="37" spans="1:3" ht="14.5">
       <c r="A37" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="14.5">
       <c r="A38" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="39" spans="1:3" ht="14.5">
       <c r="A39" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="1:3" ht="14.5">
+      <c r="A40" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-    </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-    </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A43" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A45" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-    </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A46" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A48" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-    </row>
     <row r="49" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A49" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
       <c r="A50" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A51" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-    </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A52" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
       <c r="A53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-    </row>
     <row r="55" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A55" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>77</v>
-      </c>
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
     </row>
     <row r="56" spans="1:2" ht="14.25" customHeight="1">
       <c r="A56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A57" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-    </row>
     <row r="58" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A58" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
     </row>
     <row r="59" spans="1:2" ht="14.25" customHeight="1">
       <c r="A59" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A60" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
     </row>
     <row r="61" spans="1:2" ht="14.25" customHeight="1">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="62" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+    </row>
     <row r="63" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="64" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
@@ -2194,6 +2207,7 @@
     <row r="1020" ht="14.25" customHeight="1"/>
     <row r="1021" ht="14.25" customHeight="1"/>
     <row r="1022" ht="14.25" customHeight="1"/>
+    <row r="1023" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
